--- a/tiflow-bfarm/develop/2.0.0-ballot.2/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/2.0.0-ballot.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:54:45+00:00</t>
+    <t>2026-06-15T07:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/2.0.0-ballot.2/all-profiles.xlsx
+++ b/tiflow-bfarm/develop/2.0.0-ballot.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T07:12:36+00:00</t>
+    <t>2026-06-15T07:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
